--- a/data/opportunity-scoring.xlsx
+++ b/data/opportunity-scoring.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ugyen\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Idea</t>
   </si>
@@ -73,33 +79,37 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11"/>
       <color rgb="FF1F2328"/>
       <name val="&quot;Mona Sans VF&quot;"/>
     </font>
@@ -109,7 +119,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -148,67 +158,52 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0"/>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -290,6 +285,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -316,24 +312,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -394,6 +391,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -402,17 +400,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="12.66406" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.0"/>
-    <col customWidth="1" min="7" max="7" width="37.13"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="7" max="7" width="73.10938" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,148 +452,147 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" ht="31.8" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D2" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E2" s="5">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="31.2" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C3" s="8">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E3" s="8">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="F3" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30.6" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="8">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C4" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D4" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F4" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30.6" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C5" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="8">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F5" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30.6" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D6" s="8">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="8">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F6" s="8">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="29.4" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C7" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="8">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="8">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="E10" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>